--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711818</v>
+        <v>113711805</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>56917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646982</v>
+        <v>646921</v>
       </c>
       <c r="R2" t="n">
-        <v>7037768</v>
+        <v>7037745</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711804</v>
+        <v>113713909</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646871</v>
+        <v>646798</v>
       </c>
       <c r="R3" t="n">
-        <v>7037737</v>
+        <v>7037685</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713910</v>
+        <v>113713911</v>
       </c>
       <c r="B4" t="n">
-        <v>90131</v>
+        <v>90412</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646801</v>
+        <v>646783</v>
       </c>
       <c r="R4" t="n">
-        <v>7037720</v>
+        <v>7037810</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113713928</v>
+        <v>113713929</v>
       </c>
       <c r="B5" t="n">
         <v>90131</v>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646948</v>
+        <v>646956</v>
       </c>
       <c r="R5" t="n">
-        <v>7037705</v>
+        <v>7037763</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113711807</v>
+        <v>113713917</v>
       </c>
       <c r="B6" t="n">
-        <v>97398</v>
+        <v>90131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646916</v>
+        <v>646892</v>
       </c>
       <c r="R6" t="n">
-        <v>7037675</v>
+        <v>7037818</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1177,11 +1182,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>150 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711787</v>
+        <v>113711813</v>
       </c>
       <c r="B7" t="n">
         <v>90131</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646863</v>
+        <v>646935</v>
       </c>
       <c r="R7" t="n">
-        <v>7037660</v>
+        <v>7037814</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113715157</v>
+        <v>113715160</v>
       </c>
       <c r="B8" t="n">
-        <v>90149</v>
+        <v>90131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646862</v>
+        <v>646948</v>
       </c>
       <c r="R8" t="n">
-        <v>7037725</v>
+        <v>7037706</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113715166</v>
+        <v>113711815</v>
       </c>
       <c r="B9" t="n">
-        <v>90131</v>
+        <v>97398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646938</v>
+        <v>646971</v>
       </c>
       <c r="R9" t="n">
-        <v>7037784</v>
+        <v>7037815</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1500,6 +1500,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113715171</v>
+        <v>113711822</v>
       </c>
       <c r="B10" t="n">
-        <v>90412</v>
+        <v>97398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646966</v>
+        <v>647007</v>
       </c>
       <c r="R10" t="n">
-        <v>7037793</v>
+        <v>7037798</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1606,6 +1611,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>400 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1623,7 +1633,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1634,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113715151</v>
+        <v>113713935</v>
       </c>
       <c r="B11" t="n">
         <v>90412</v>
@@ -1674,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646826</v>
+        <v>646966</v>
       </c>
       <c r="R11" t="n">
-        <v>7037814</v>
+        <v>7037793</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711496</v>
+        <v>113713937</v>
       </c>
       <c r="B12" t="n">
-        <v>97398</v>
+        <v>90316</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647016</v>
+        <v>646993</v>
       </c>
       <c r="R12" t="n">
-        <v>7037806</v>
+        <v>7037776</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1818,11 +1828,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>100 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1840,7 +1845,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1851,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711495</v>
+        <v>113715152</v>
       </c>
       <c r="B13" t="n">
-        <v>97398</v>
+        <v>90131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647007</v>
+        <v>646856</v>
       </c>
       <c r="R13" t="n">
-        <v>7037798</v>
+        <v>7037838</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1929,11 +1934,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>400 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113713918</v>
+        <v>113711797</v>
       </c>
       <c r="B14" t="n">
-        <v>90131</v>
+        <v>90412</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646869</v>
+        <v>646826</v>
       </c>
       <c r="R14" t="n">
-        <v>7037783</v>
+        <v>7037814</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113715174</v>
+        <v>113715163</v>
       </c>
       <c r="B15" t="n">
-        <v>97398</v>
+        <v>90131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646995</v>
+        <v>646932</v>
       </c>
       <c r="R15" t="n">
-        <v>7037777</v>
+        <v>7037691</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2144,11 +2144,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113715149</v>
+        <v>113711794</v>
       </c>
       <c r="B16" t="n">
-        <v>90131</v>
+        <v>90316</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646800</v>
+        <v>646778</v>
       </c>
       <c r="R16" t="n">
-        <v>7037819</v>
+        <v>7037818</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2274,7 +2269,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2285,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113715163</v>
+        <v>113711494</v>
       </c>
       <c r="B17" t="n">
-        <v>90131</v>
+        <v>97398</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646932</v>
+        <v>646993</v>
       </c>
       <c r="R17" t="n">
-        <v>7037691</v>
+        <v>7037796</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2363,6 +2358,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2000 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113711802</v>
+        <v>113713925</v>
       </c>
       <c r="B18" t="n">
-        <v>90142</v>
+        <v>97398</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646857</v>
+        <v>646916</v>
       </c>
       <c r="R18" t="n">
-        <v>7037736</v>
+        <v>7037675</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2469,6 +2469,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>150 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2486,7 +2491,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2497,7 +2502,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113713917</v>
+        <v>113713919</v>
       </c>
       <c r="B19" t="n">
         <v>90131</v>
@@ -2537,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646892</v>
+        <v>646842</v>
       </c>
       <c r="R19" t="n">
-        <v>7037818</v>
+        <v>7037747</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113715159</v>
+        <v>113715168</v>
       </c>
       <c r="B20" t="n">
-        <v>56917</v>
+        <v>90412</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2620,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646921</v>
+        <v>646943</v>
       </c>
       <c r="R20" t="n">
-        <v>7037745</v>
+        <v>7037813</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2679,11 +2684,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,7 +2714,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113715165</v>
+        <v>113711800</v>
       </c>
       <c r="B21" t="n">
         <v>90131</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646956</v>
+        <v>646869</v>
       </c>
       <c r="R21" t="n">
-        <v>7037763</v>
+        <v>7037783</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113713937</v>
+        <v>113711810</v>
       </c>
       <c r="B22" t="n">
-        <v>90316</v>
+        <v>90131</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646993</v>
+        <v>646948</v>
       </c>
       <c r="R22" t="n">
-        <v>7037776</v>
+        <v>7037705</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113713939</v>
+        <v>113713910</v>
       </c>
       <c r="B23" t="n">
-        <v>97398</v>
+        <v>90131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646993</v>
+        <v>646801</v>
       </c>
       <c r="R23" t="n">
-        <v>7037796</v>
+        <v>7037720</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3002,11 +3002,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3037,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113713907</v>
+        <v>113713930</v>
       </c>
       <c r="B24" t="n">
-        <v>78201</v>
+        <v>90131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3053,21 +3048,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646869</v>
+        <v>646938</v>
       </c>
       <c r="R24" t="n">
-        <v>7037654</v>
+        <v>7037784</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3143,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113715168</v>
+        <v>113713913</v>
       </c>
       <c r="B25" t="n">
-        <v>90412</v>
+        <v>90131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3159,21 +3154,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3183,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646943</v>
+        <v>646800</v>
       </c>
       <c r="R25" t="n">
-        <v>7037813</v>
+        <v>7037819</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3249,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113713934</v>
+        <v>113715172</v>
       </c>
       <c r="B26" t="n">
-        <v>97398</v>
+        <v>90131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646978</v>
+        <v>646982</v>
       </c>
       <c r="R26" t="n">
-        <v>7037805</v>
+        <v>7037768</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,11 +3320,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3360,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113713914</v>
+        <v>113711802</v>
       </c>
       <c r="B27" t="n">
-        <v>56826</v>
+        <v>90142</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,25 +3362,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646810</v>
+        <v>646857</v>
       </c>
       <c r="R27" t="n">
-        <v>7037810</v>
+        <v>7037736</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3438,11 +3428,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>En hona</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3445,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3471,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113715160</v>
+        <v>113711790</v>
       </c>
       <c r="B28" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3487,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3496,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646948</v>
+        <v>646842</v>
       </c>
       <c r="R28" t="n">
-        <v>7037706</v>
+        <v>7037658</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3566,7 +3551,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3577,10 +3562,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113715152</v>
+        <v>113715174</v>
       </c>
       <c r="B29" t="n">
-        <v>90131</v>
+        <v>97398</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3589,25 +3574,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3617,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646856</v>
+        <v>646995</v>
       </c>
       <c r="R29" t="n">
-        <v>7037838</v>
+        <v>7037777</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3653,6 +3638,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3683,7 +3673,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113711791</v>
+        <v>113711788</v>
       </c>
       <c r="B30" t="n">
         <v>78201</v>
@@ -3723,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646798</v>
+        <v>646869</v>
       </c>
       <c r="R30" t="n">
-        <v>7037685</v>
+        <v>7037654</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3789,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113711794</v>
+        <v>113711823</v>
       </c>
       <c r="B31" t="n">
-        <v>90316</v>
+        <v>97398</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3805,21 +3795,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3829,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646778</v>
+        <v>647016</v>
       </c>
       <c r="R31" t="n">
-        <v>7037818</v>
+        <v>7037806</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3865,6 +3855,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>100 orkidéer ca</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113715144</v>
+        <v>113715142</v>
       </c>
       <c r="B32" t="n">
-        <v>78201</v>
+        <v>90131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3911,21 +3906,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3930,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646842</v>
+        <v>646863</v>
       </c>
       <c r="R32" t="n">
-        <v>7037658</v>
+        <v>7037660</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4001,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113713919</v>
+        <v>113711803</v>
       </c>
       <c r="B33" t="n">
-        <v>90131</v>
+        <v>90149</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4017,21 +4012,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4041,10 +4036,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646842</v>
+        <v>646862</v>
       </c>
       <c r="R33" t="n">
-        <v>7037747</v>
+        <v>7037725</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4096,7 +4091,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4107,7 +4102,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113715169</v>
+        <v>113711816</v>
       </c>
       <c r="B34" t="n">
         <v>97398</v>
@@ -4147,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646971</v>
+        <v>646978</v>
       </c>
       <c r="R34" t="n">
-        <v>7037815</v>
+        <v>7037805</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4187,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>250 orkidéer ca</t>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4207,7 +4202,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4218,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113711793</v>
+        <v>113711804</v>
       </c>
       <c r="B35" t="n">
-        <v>90412</v>
+        <v>90131</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4234,21 +4229,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4258,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646783</v>
+        <v>646871</v>
       </c>
       <c r="R35" t="n">
-        <v>7037810</v>
+        <v>7037737</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4324,10 +4319,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113715167</v>
+        <v>113713914</v>
       </c>
       <c r="B36" t="n">
-        <v>90131</v>
+        <v>56826</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4340,21 +4335,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4364,10 +4359,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646935</v>
+        <v>646810</v>
       </c>
       <c r="R36" t="n">
-        <v>7037814</v>
+        <v>7037810</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4400,6 +4395,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>En hona</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711805</v>
+        <v>113713910</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646921</v>
+        <v>646801</v>
       </c>
       <c r="R2" t="n">
-        <v>7037745</v>
+        <v>7037720</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,11 +753,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713909</v>
+        <v>113713916</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646798</v>
+        <v>646856</v>
       </c>
       <c r="R3" t="n">
-        <v>7037685</v>
+        <v>7037838</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713911</v>
+        <v>113713935</v>
       </c>
       <c r="B4" t="n">
-        <v>90412</v>
+        <v>90416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646783</v>
+        <v>646966</v>
       </c>
       <c r="R4" t="n">
-        <v>7037810</v>
+        <v>7037793</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113713929</v>
+        <v>113711797</v>
       </c>
       <c r="B5" t="n">
-        <v>90131</v>
+        <v>90416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646956</v>
+        <v>646826</v>
       </c>
       <c r="R5" t="n">
-        <v>7037763</v>
+        <v>7037814</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113713917</v>
+        <v>113713908</v>
       </c>
       <c r="B6" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646892</v>
+        <v>646842</v>
       </c>
       <c r="R6" t="n">
-        <v>7037818</v>
+        <v>7037658</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711813</v>
+        <v>113713923</v>
       </c>
       <c r="B7" t="n">
-        <v>90131</v>
+        <v>56917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646935</v>
+        <v>646921</v>
       </c>
       <c r="R7" t="n">
-        <v>7037814</v>
+        <v>7037745</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1288,6 +1283,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113715160</v>
+        <v>113711796</v>
       </c>
       <c r="B8" t="n">
-        <v>90131</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646948</v>
+        <v>646810</v>
       </c>
       <c r="R8" t="n">
-        <v>7037706</v>
+        <v>7037810</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,6 +1394,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En hona</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1422,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711815</v>
+        <v>113711822</v>
       </c>
       <c r="B9" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646971</v>
+        <v>647007</v>
       </c>
       <c r="R9" t="n">
-        <v>7037815</v>
+        <v>7037798</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1502,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>250 orkidéer ca</t>
+          <t>400 orkidéer ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711822</v>
+        <v>113713939</v>
       </c>
       <c r="B10" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>647007</v>
+        <v>646993</v>
       </c>
       <c r="R10" t="n">
-        <v>7037798</v>
+        <v>7037796</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,7 +1618,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>400 orkidéer ca</t>
+          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1638,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1644,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113713935</v>
+        <v>113711794</v>
       </c>
       <c r="B11" t="n">
-        <v>90412</v>
+        <v>90320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646966</v>
+        <v>646778</v>
       </c>
       <c r="R11" t="n">
-        <v>7037793</v>
+        <v>7037818</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,7 +1744,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113713937</v>
+        <v>113711806</v>
       </c>
       <c r="B12" t="n">
-        <v>90316</v>
+        <v>90135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646993</v>
+        <v>646948</v>
       </c>
       <c r="R12" t="n">
-        <v>7037776</v>
+        <v>7037706</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1856,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113715152</v>
+        <v>113715161</v>
       </c>
       <c r="B13" t="n">
-        <v>90131</v>
+        <v>97402</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>646856</v>
+        <v>646916</v>
       </c>
       <c r="R13" t="n">
-        <v>7037838</v>
+        <v>7037675</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,6 +1937,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>150 orkidéer ca</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711797</v>
+        <v>113713934</v>
       </c>
       <c r="B14" t="n">
-        <v>90412</v>
+        <v>97402</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646826</v>
+        <v>646978</v>
       </c>
       <c r="R14" t="n">
-        <v>7037814</v>
+        <v>7037805</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2040,6 +2050,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2057,7 +2072,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2068,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113715163</v>
+        <v>113711788</v>
       </c>
       <c r="B15" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2099,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646932</v>
+        <v>646869</v>
       </c>
       <c r="R15" t="n">
-        <v>7037691</v>
+        <v>7037654</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2178,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2174,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711794</v>
+        <v>113711802</v>
       </c>
       <c r="B16" t="n">
-        <v>90316</v>
+        <v>90146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,25 +2201,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646778</v>
+        <v>646857</v>
       </c>
       <c r="R16" t="n">
-        <v>7037818</v>
+        <v>7037736</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711494</v>
+        <v>113713917</v>
       </c>
       <c r="B17" t="n">
-        <v>97398</v>
+        <v>90135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2307,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646993</v>
+        <v>646892</v>
       </c>
       <c r="R17" t="n">
-        <v>7037796</v>
+        <v>7037818</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2358,11 +2373,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2000 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2380,7 +2390,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2391,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113713925</v>
+        <v>113715169</v>
       </c>
       <c r="B18" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646916</v>
+        <v>646971</v>
       </c>
       <c r="R18" t="n">
-        <v>7037675</v>
+        <v>7037815</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2471,7 +2481,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>150 orkidéer ca</t>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113713919</v>
+        <v>113713941</v>
       </c>
       <c r="B19" t="n">
-        <v>90131</v>
+        <v>97402</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2524,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646842</v>
+        <v>647016</v>
       </c>
       <c r="R19" t="n">
-        <v>7037747</v>
+        <v>7037806</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2578,6 +2588,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>100 orkidéer ca</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113715168</v>
+        <v>113711795</v>
       </c>
       <c r="B20" t="n">
-        <v>90412</v>
+        <v>90135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2648,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646943</v>
+        <v>646800</v>
       </c>
       <c r="R20" t="n">
-        <v>7037813</v>
+        <v>7037819</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2703,7 +2718,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2714,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113711800</v>
+        <v>113711803</v>
       </c>
       <c r="B21" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,21 +2745,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2769,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646869</v>
+        <v>646862</v>
       </c>
       <c r="R21" t="n">
-        <v>7037783</v>
+        <v>7037725</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2820,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113711810</v>
+        <v>113711787</v>
       </c>
       <c r="B22" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2860,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646948</v>
+        <v>646863</v>
       </c>
       <c r="R22" t="n">
-        <v>7037705</v>
+        <v>7037660</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2926,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113713910</v>
+        <v>113715154</v>
       </c>
       <c r="B23" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646801</v>
+        <v>646869</v>
       </c>
       <c r="R23" t="n">
-        <v>7037720</v>
+        <v>7037783</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3032,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113713930</v>
+        <v>113711811</v>
       </c>
       <c r="B24" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3072,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646938</v>
+        <v>646956</v>
       </c>
       <c r="R24" t="n">
-        <v>7037784</v>
+        <v>7037763</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3127,7 +3142,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3138,10 +3153,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113713913</v>
+        <v>113715164</v>
       </c>
       <c r="B25" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646800</v>
+        <v>646948</v>
       </c>
       <c r="R25" t="n">
-        <v>7037819</v>
+        <v>7037705</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113715172</v>
+        <v>113713936</v>
       </c>
       <c r="B26" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3350,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113711802</v>
+        <v>113713927</v>
       </c>
       <c r="B27" t="n">
-        <v>90142</v>
+        <v>90135</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,25 +3377,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3390,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646857</v>
+        <v>646932</v>
       </c>
       <c r="R27" t="n">
-        <v>7037736</v>
+        <v>7037691</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3445,7 +3460,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3456,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113711790</v>
+        <v>113713919</v>
       </c>
       <c r="B28" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,21 +3487,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,7 +3514,7 @@
         <v>646842</v>
       </c>
       <c r="R28" t="n">
-        <v>7037658</v>
+        <v>7037747</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3551,7 +3566,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3562,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113715174</v>
+        <v>113713922</v>
       </c>
       <c r="B29" t="n">
-        <v>97398</v>
+        <v>90135</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,25 +3589,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646995</v>
+        <v>646871</v>
       </c>
       <c r="R29" t="n">
-        <v>7037777</v>
+        <v>7037737</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3638,11 +3653,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3673,10 +3683,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113711788</v>
+        <v>113713938</v>
       </c>
       <c r="B30" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,25 +3695,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646869</v>
+        <v>646995</v>
       </c>
       <c r="R30" t="n">
-        <v>7037654</v>
+        <v>7037777</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3751,6 +3761,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3768,7 +3783,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3779,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113711823</v>
+        <v>113711814</v>
       </c>
       <c r="B31" t="n">
-        <v>97398</v>
+        <v>90416</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,25 +3806,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3819,10 +3834,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>647016</v>
+        <v>646943</v>
       </c>
       <c r="R31" t="n">
-        <v>7037806</v>
+        <v>7037813</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3855,11 +3870,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>100 orkidéer ca</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113715142</v>
+        <v>113711812</v>
       </c>
       <c r="B32" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3930,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646863</v>
+        <v>646938</v>
       </c>
       <c r="R32" t="n">
-        <v>7037660</v>
+        <v>7037784</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3985,7 +3995,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3996,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113711803</v>
+        <v>113715167</v>
       </c>
       <c r="B33" t="n">
-        <v>90149</v>
+        <v>90135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4012,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4036,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646862</v>
+        <v>646935</v>
       </c>
       <c r="R33" t="n">
-        <v>7037725</v>
+        <v>7037814</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4091,7 +4101,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4102,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113711816</v>
+        <v>113713909</v>
       </c>
       <c r="B34" t="n">
-        <v>97398</v>
+        <v>78201</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4114,25 +4124,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646978</v>
+        <v>646798</v>
       </c>
       <c r="R34" t="n">
-        <v>7037805</v>
+        <v>7037685</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4180,11 +4190,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4202,7 +4207,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4213,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113711804</v>
+        <v>113711819</v>
       </c>
       <c r="B35" t="n">
-        <v>90131</v>
+        <v>90320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4225,25 +4230,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646871</v>
+        <v>646993</v>
       </c>
       <c r="R35" t="n">
-        <v>7037737</v>
+        <v>7037776</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4319,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113713914</v>
+        <v>113713911</v>
       </c>
       <c r="B36" t="n">
-        <v>56826</v>
+        <v>90416</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4335,21 +4340,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4359,7 +4364,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646810</v>
+        <v>646783</v>
       </c>
       <c r="R36" t="n">
         <v>7037810</v>
@@ -4395,11 +4400,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>En hona</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713910</v>
+        <v>113713936</v>
       </c>
       <c r="B2" t="n">
         <v>90135</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646801</v>
+        <v>646982</v>
       </c>
       <c r="R2" t="n">
-        <v>7037720</v>
+        <v>7037768</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713916</v>
+        <v>113713939</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646856</v>
+        <v>646993</v>
       </c>
       <c r="R3" t="n">
-        <v>7037838</v>
+        <v>7037796</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713935</v>
+        <v>113713934</v>
       </c>
       <c r="B4" t="n">
-        <v>90416</v>
+        <v>97402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646966</v>
+        <v>646978</v>
       </c>
       <c r="R4" t="n">
-        <v>7037793</v>
+        <v>7037805</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113711797</v>
+        <v>113713912</v>
       </c>
       <c r="B5" t="n">
-        <v>90416</v>
+        <v>90320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646826</v>
+        <v>646778</v>
       </c>
       <c r="R5" t="n">
-        <v>7037814</v>
+        <v>7037818</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1098,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113713908</v>
+        <v>113715154</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646842</v>
+        <v>646869</v>
       </c>
       <c r="R6" t="n">
-        <v>7037658</v>
+        <v>7037783</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113713923</v>
+        <v>113715155</v>
       </c>
       <c r="B7" t="n">
-        <v>56917</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646921</v>
+        <v>646842</v>
       </c>
       <c r="R7" t="n">
-        <v>7037745</v>
+        <v>7037747</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113711796</v>
+        <v>113715145</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646810</v>
+        <v>646798</v>
       </c>
       <c r="R8" t="n">
-        <v>7037810</v>
+        <v>7037685</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,11 +1399,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En hona</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1427,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711822</v>
+        <v>113715174</v>
       </c>
       <c r="B9" t="n">
         <v>97402</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647007</v>
+        <v>646995</v>
       </c>
       <c r="R9" t="n">
-        <v>7037798</v>
+        <v>7037777</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>400 orkidéer ca</t>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113713939</v>
+        <v>113713929</v>
       </c>
       <c r="B10" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646993</v>
+        <v>646956</v>
       </c>
       <c r="R10" t="n">
-        <v>7037796</v>
+        <v>7037763</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1614,11 +1614,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711794</v>
+        <v>113711793</v>
       </c>
       <c r="B11" t="n">
-        <v>90320</v>
+        <v>90416</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646778</v>
+        <v>646783</v>
       </c>
       <c r="R11" t="n">
-        <v>7037818</v>
+        <v>7037810</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113711806</v>
+        <v>113713935</v>
       </c>
       <c r="B12" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646948</v>
+        <v>646966</v>
       </c>
       <c r="R12" t="n">
-        <v>7037706</v>
+        <v>7037793</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1861,7 +1856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113715161</v>
+        <v>113711823</v>
       </c>
       <c r="B13" t="n">
         <v>97402</v>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>646916</v>
+        <v>647016</v>
       </c>
       <c r="R13" t="n">
-        <v>7037675</v>
+        <v>7037806</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1941,7 +1936,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>150 orkidéer ca</t>
+          <t>100 orkidéer ca</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,7 +1956,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113713934</v>
+        <v>113711802</v>
       </c>
       <c r="B14" t="n">
-        <v>97402</v>
+        <v>90146</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646978</v>
+        <v>646857</v>
       </c>
       <c r="R14" t="n">
-        <v>7037805</v>
+        <v>7037736</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2050,11 +2045,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2083,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711788</v>
+        <v>113715143</v>
       </c>
       <c r="B15" t="n">
         <v>78201</v>
@@ -2178,7 +2168,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2189,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711802</v>
+        <v>113711796</v>
       </c>
       <c r="B16" t="n">
-        <v>90146</v>
+        <v>56826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2229,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646857</v>
+        <v>646810</v>
       </c>
       <c r="R16" t="n">
-        <v>7037736</v>
+        <v>7037810</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2265,6 +2255,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En hona</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113713917</v>
+        <v>113711798</v>
       </c>
       <c r="B17" t="n">
         <v>90135</v>
@@ -2335,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646892</v>
+        <v>646856</v>
       </c>
       <c r="R17" t="n">
-        <v>7037818</v>
+        <v>7037838</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,7 +2385,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2401,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113715169</v>
+        <v>113713906</v>
       </c>
       <c r="B18" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646971</v>
+        <v>646863</v>
       </c>
       <c r="R18" t="n">
-        <v>7037815</v>
+        <v>7037660</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,11 +2472,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113713941</v>
+        <v>113713927</v>
       </c>
       <c r="B19" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>647016</v>
+        <v>646932</v>
       </c>
       <c r="R19" t="n">
-        <v>7037806</v>
+        <v>7037691</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2588,11 +2578,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>100 orkidéer ca</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,7 +2608,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113711795</v>
+        <v>113713913</v>
       </c>
       <c r="B20" t="n">
         <v>90135</v>
@@ -2718,7 +2703,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2729,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113711803</v>
+        <v>113711822</v>
       </c>
       <c r="B21" t="n">
-        <v>90153</v>
+        <v>97402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646862</v>
+        <v>647007</v>
       </c>
       <c r="R21" t="n">
-        <v>7037725</v>
+        <v>7037798</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2805,6 +2790,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>400 orkidéer ca</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113711787</v>
+        <v>113715159</v>
       </c>
       <c r="B22" t="n">
-        <v>90135</v>
+        <v>56917</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,25 +2837,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646863</v>
+        <v>646921</v>
       </c>
       <c r="R22" t="n">
-        <v>7037660</v>
+        <v>7037745</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2913,6 +2903,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2941,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113715154</v>
+        <v>113715157</v>
       </c>
       <c r="B23" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646869</v>
+        <v>646862</v>
       </c>
       <c r="R23" t="n">
-        <v>7037783</v>
+        <v>7037725</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3047,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113711811</v>
+        <v>113711810</v>
       </c>
       <c r="B24" t="n">
         <v>90135</v>
@@ -3087,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646956</v>
+        <v>646948</v>
       </c>
       <c r="R24" t="n">
-        <v>7037763</v>
+        <v>7037705</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3153,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113715164</v>
+        <v>113715161</v>
       </c>
       <c r="B25" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,25 +3160,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646948</v>
+        <v>646916</v>
       </c>
       <c r="R25" t="n">
-        <v>7037705</v>
+        <v>7037675</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3229,6 +3224,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>150 orkidéer ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,7 +3259,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113713936</v>
+        <v>113713922</v>
       </c>
       <c r="B26" t="n">
         <v>90135</v>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646982</v>
+        <v>646871</v>
       </c>
       <c r="R26" t="n">
-        <v>7037768</v>
+        <v>7037737</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113713927</v>
+        <v>113713910</v>
       </c>
       <c r="B27" t="n">
         <v>90135</v>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646932</v>
+        <v>646801</v>
       </c>
       <c r="R27" t="n">
-        <v>7037691</v>
+        <v>7037720</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3471,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113713919</v>
+        <v>113715160</v>
       </c>
       <c r="B28" t="n">
         <v>90135</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646842</v>
+        <v>646948</v>
       </c>
       <c r="R28" t="n">
-        <v>7037747</v>
+        <v>7037706</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113713922</v>
+        <v>113711797</v>
       </c>
       <c r="B29" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,21 +3593,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646871</v>
+        <v>646826</v>
       </c>
       <c r="R29" t="n">
-        <v>7037737</v>
+        <v>7037814</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3683,7 +3683,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113713938</v>
+        <v>113713933</v>
       </c>
       <c r="B30" t="n">
         <v>97402</v>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646995</v>
+        <v>646971</v>
       </c>
       <c r="R30" t="n">
-        <v>7037777</v>
+        <v>7037815</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113711814</v>
+        <v>113715168</v>
       </c>
       <c r="B31" t="n">
         <v>90416</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3900,7 +3900,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113711812</v>
+        <v>113713917</v>
       </c>
       <c r="B32" t="n">
         <v>90135</v>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646938</v>
+        <v>646892</v>
       </c>
       <c r="R32" t="n">
-        <v>7037784</v>
+        <v>7037818</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4006,7 +4006,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113715167</v>
+        <v>113713931</v>
       </c>
       <c r="B33" t="n">
         <v>90135</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113713909</v>
+        <v>113713908</v>
       </c>
       <c r="B34" t="n">
         <v>78201</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646798</v>
+        <v>646842</v>
       </c>
       <c r="R34" t="n">
-        <v>7037685</v>
+        <v>7037658</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113711819</v>
+        <v>113711812</v>
       </c>
       <c r="B35" t="n">
-        <v>90320</v>
+        <v>90135</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4230,25 +4230,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646993</v>
+        <v>646938</v>
       </c>
       <c r="R35" t="n">
-        <v>7037776</v>
+        <v>7037784</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4324,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113713911</v>
+        <v>113711819</v>
       </c>
       <c r="B36" t="n">
-        <v>90416</v>
+        <v>90320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4336,25 +4336,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646783</v>
+        <v>646993</v>
       </c>
       <c r="R36" t="n">
-        <v>7037810</v>
+        <v>7037776</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713936</v>
+        <v>113713937</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646982</v>
+        <v>646993</v>
       </c>
       <c r="R2" t="n">
-        <v>7037768</v>
+        <v>7037776</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713939</v>
+        <v>113713923</v>
       </c>
       <c r="B3" t="n">
-        <v>97402</v>
+        <v>56917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646993</v>
+        <v>646921</v>
       </c>
       <c r="R3" t="n">
-        <v>7037796</v>
+        <v>7037745</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2000 orkidéer ca</t>
+          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713934</v>
+        <v>113711822</v>
       </c>
       <c r="B4" t="n">
         <v>97402</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646978</v>
+        <v>647007</v>
       </c>
       <c r="R4" t="n">
-        <v>7037805</v>
+        <v>7037798</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>200 orkidéer ca</t>
+          <t>400 orkidéer ca</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113713912</v>
+        <v>113715172</v>
       </c>
       <c r="B5" t="n">
-        <v>90320</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646778</v>
+        <v>646982</v>
       </c>
       <c r="R5" t="n">
-        <v>7037818</v>
+        <v>7037768</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113715154</v>
+        <v>113715164</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646869</v>
+        <v>646948</v>
       </c>
       <c r="R6" t="n">
-        <v>7037783</v>
+        <v>7037705</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113715155</v>
+        <v>113715166</v>
       </c>
       <c r="B7" t="n">
         <v>90135</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646842</v>
+        <v>646938</v>
       </c>
       <c r="R7" t="n">
-        <v>7037747</v>
+        <v>7037784</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113715145</v>
+        <v>113715155</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646798</v>
+        <v>646842</v>
       </c>
       <c r="R8" t="n">
-        <v>7037685</v>
+        <v>7037747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113715174</v>
+        <v>113713935</v>
       </c>
       <c r="B9" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646995</v>
+        <v>646966</v>
       </c>
       <c r="R9" t="n">
-        <v>7037777</v>
+        <v>7037793</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113713929</v>
+        <v>113713906</v>
       </c>
       <c r="B10" t="n">
         <v>90135</v>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646956</v>
+        <v>646863</v>
       </c>
       <c r="R10" t="n">
-        <v>7037763</v>
+        <v>7037660</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113711793</v>
+        <v>113715167</v>
       </c>
       <c r="B11" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646783</v>
+        <v>646935</v>
       </c>
       <c r="R11" t="n">
-        <v>7037810</v>
+        <v>7037814</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,7 +1734,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1750,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113713935</v>
+        <v>113715168</v>
       </c>
       <c r="B12" t="n">
         <v>90416</v>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646966</v>
+        <v>646943</v>
       </c>
       <c r="R12" t="n">
-        <v>7037793</v>
+        <v>7037813</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711823</v>
+        <v>113713927</v>
       </c>
       <c r="B13" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647016</v>
+        <v>646932</v>
       </c>
       <c r="R13" t="n">
-        <v>7037806</v>
+        <v>7037691</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1934,11 +1929,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>100 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1956,7 +1946,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1967,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711802</v>
+        <v>113711790</v>
       </c>
       <c r="B14" t="n">
-        <v>90146</v>
+        <v>78201</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646857</v>
+        <v>646842</v>
       </c>
       <c r="R14" t="n">
-        <v>7037736</v>
+        <v>7037658</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113715143</v>
+        <v>113713939</v>
       </c>
       <c r="B15" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646869</v>
+        <v>646993</v>
       </c>
       <c r="R15" t="n">
-        <v>7037654</v>
+        <v>7037796</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,6 +2139,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711796</v>
+        <v>113711797</v>
       </c>
       <c r="B16" t="n">
-        <v>56826</v>
+        <v>90416</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646810</v>
+        <v>646826</v>
       </c>
       <c r="R16" t="n">
-        <v>7037810</v>
+        <v>7037814</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2255,11 +2250,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En hona</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711798</v>
+        <v>113715147</v>
       </c>
       <c r="B17" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646856</v>
+        <v>646783</v>
       </c>
       <c r="R17" t="n">
-        <v>7037838</v>
+        <v>7037810</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2385,7 +2375,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2396,7 +2386,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113713906</v>
+        <v>113715160</v>
       </c>
       <c r="B18" t="n">
         <v>90135</v>
@@ -2436,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646863</v>
+        <v>646948</v>
       </c>
       <c r="R18" t="n">
-        <v>7037660</v>
+        <v>7037706</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,7 +2492,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113713927</v>
+        <v>113713917</v>
       </c>
       <c r="B19" t="n">
         <v>90135</v>
@@ -2542,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646932</v>
+        <v>646892</v>
       </c>
       <c r="R19" t="n">
-        <v>7037691</v>
+        <v>7037818</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,7 +2598,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113713913</v>
+        <v>113715146</v>
       </c>
       <c r="B20" t="n">
         <v>90135</v>
@@ -2648,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646800</v>
+        <v>646801</v>
       </c>
       <c r="R20" t="n">
-        <v>7037819</v>
+        <v>7037720</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2714,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113711822</v>
+        <v>113715145</v>
       </c>
       <c r="B21" t="n">
-        <v>97402</v>
+        <v>78201</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2726,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2754,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>647007</v>
+        <v>646798</v>
       </c>
       <c r="R21" t="n">
-        <v>7037798</v>
+        <v>7037685</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,11 +2782,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>400 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2814,7 +2799,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2825,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113715159</v>
+        <v>113711788</v>
       </c>
       <c r="B22" t="n">
-        <v>56917</v>
+        <v>78201</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,25 +2822,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646921</v>
+        <v>646869</v>
       </c>
       <c r="R22" t="n">
-        <v>7037745</v>
+        <v>7037654</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2903,11 +2888,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2905,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2936,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113715157</v>
+        <v>113713925</v>
       </c>
       <c r="B23" t="n">
-        <v>90153</v>
+        <v>97402</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,25 +2928,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646862</v>
+        <v>646916</v>
       </c>
       <c r="R23" t="n">
-        <v>7037725</v>
+        <v>7037675</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,6 +2992,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>150 orkidéer ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113711810</v>
+        <v>113711823</v>
       </c>
       <c r="B24" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3054,25 +3039,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646948</v>
+        <v>647016</v>
       </c>
       <c r="R24" t="n">
-        <v>7037705</v>
+        <v>7037806</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,6 +3103,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>100 orkidéer ca</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3148,7 +3138,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113715161</v>
+        <v>113711820</v>
       </c>
       <c r="B25" t="n">
         <v>97402</v>
@@ -3188,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646916</v>
+        <v>646995</v>
       </c>
       <c r="R25" t="n">
-        <v>7037675</v>
+        <v>7037777</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3228,7 +3218,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>150 orkidéer ca</t>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,7 +3238,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3259,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113713922</v>
+        <v>113715157</v>
       </c>
       <c r="B26" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,21 +3265,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3299,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646871</v>
+        <v>646862</v>
       </c>
       <c r="R26" t="n">
-        <v>7037737</v>
+        <v>7037725</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3365,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113713910</v>
+        <v>113711802</v>
       </c>
       <c r="B27" t="n">
-        <v>90135</v>
+        <v>90146</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3377,25 +3367,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3405,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646801</v>
+        <v>646857</v>
       </c>
       <c r="R27" t="n">
-        <v>7037720</v>
+        <v>7037736</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3460,7 +3450,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3471,7 +3461,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113715160</v>
+        <v>113711798</v>
       </c>
       <c r="B28" t="n">
         <v>90135</v>
@@ -3511,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646948</v>
+        <v>646856</v>
       </c>
       <c r="R28" t="n">
-        <v>7037706</v>
+        <v>7037838</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3566,7 +3556,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3577,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113711797</v>
+        <v>113713922</v>
       </c>
       <c r="B29" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,21 +3583,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3617,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646826</v>
+        <v>646871</v>
       </c>
       <c r="R29" t="n">
-        <v>7037814</v>
+        <v>7037737</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3672,7 +3662,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3683,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113713933</v>
+        <v>113715165</v>
       </c>
       <c r="B30" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,25 +3685,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3723,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646971</v>
+        <v>646956</v>
       </c>
       <c r="R30" t="n">
-        <v>7037815</v>
+        <v>7037763</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3759,11 +3749,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113715168</v>
+        <v>113713912</v>
       </c>
       <c r="B31" t="n">
-        <v>90416</v>
+        <v>90320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3806,25 +3791,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3834,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646943</v>
+        <v>646778</v>
       </c>
       <c r="R31" t="n">
-        <v>7037813</v>
+        <v>7037818</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3900,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113713917</v>
+        <v>113715170</v>
       </c>
       <c r="B32" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3912,25 +3897,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3940,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646892</v>
+        <v>646978</v>
       </c>
       <c r="R32" t="n">
-        <v>7037818</v>
+        <v>7037805</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3976,6 +3961,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,7 +3996,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113713931</v>
+        <v>113715154</v>
       </c>
       <c r="B33" t="n">
         <v>90135</v>
@@ -4046,10 +4036,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646935</v>
+        <v>646869</v>
       </c>
       <c r="R33" t="n">
-        <v>7037814</v>
+        <v>7037783</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,10 +4102,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113713908</v>
+        <v>113711796</v>
       </c>
       <c r="B34" t="n">
-        <v>78201</v>
+        <v>56826</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4128,21 +4118,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646842</v>
+        <v>646810</v>
       </c>
       <c r="R34" t="n">
-        <v>7037658</v>
+        <v>7037810</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4190,6 +4180,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>En hona</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4207,7 +4202,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4218,7 +4213,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113711812</v>
+        <v>113715149</v>
       </c>
       <c r="B35" t="n">
         <v>90135</v>
@@ -4258,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646938</v>
+        <v>646800</v>
       </c>
       <c r="R35" t="n">
-        <v>7037784</v>
+        <v>7037819</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4313,7 +4308,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4324,10 +4319,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113711819</v>
+        <v>113711815</v>
       </c>
       <c r="B36" t="n">
-        <v>90320</v>
+        <v>97402</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4340,21 +4335,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4364,10 +4359,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646993</v>
+        <v>646971</v>
       </c>
       <c r="R36" t="n">
-        <v>7037776</v>
+        <v>7037815</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4400,6 +4395,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713937</v>
+        <v>113715158</v>
       </c>
       <c r="B2" t="n">
-        <v>90320</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646993</v>
+        <v>646871</v>
       </c>
       <c r="R2" t="n">
-        <v>7037776</v>
+        <v>7037737</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713923</v>
+        <v>113711810</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646921</v>
+        <v>646948</v>
       </c>
       <c r="R3" t="n">
-        <v>7037745</v>
+        <v>7037705</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,11 +859,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711822</v>
+        <v>113713910</v>
       </c>
       <c r="B4" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647007</v>
+        <v>646801</v>
       </c>
       <c r="R4" t="n">
-        <v>7037798</v>
+        <v>7037720</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,11 +965,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>400 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -992,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1003,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113715172</v>
+        <v>113715152</v>
       </c>
       <c r="B5" t="n">
         <v>90135</v>
@@ -1043,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646982</v>
+        <v>646856</v>
       </c>
       <c r="R5" t="n">
-        <v>7037768</v>
+        <v>7037838</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113715164</v>
+        <v>113715170</v>
       </c>
       <c r="B6" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646948</v>
+        <v>646978</v>
       </c>
       <c r="R6" t="n">
-        <v>7037705</v>
+        <v>7037805</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113715166</v>
+        <v>113711820</v>
       </c>
       <c r="B7" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646938</v>
+        <v>646995</v>
       </c>
       <c r="R7" t="n">
-        <v>7037784</v>
+        <v>7037777</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,6 +1288,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113715155</v>
+        <v>113715145</v>
       </c>
       <c r="B8" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646842</v>
+        <v>646798</v>
       </c>
       <c r="R8" t="n">
-        <v>7037747</v>
+        <v>7037685</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113713935</v>
+        <v>113711802</v>
       </c>
       <c r="B9" t="n">
-        <v>90416</v>
+        <v>90146</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646966</v>
+        <v>646857</v>
       </c>
       <c r="R9" t="n">
-        <v>7037793</v>
+        <v>7037736</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113713906</v>
+        <v>113711805</v>
       </c>
       <c r="B10" t="n">
-        <v>90135</v>
+        <v>56917</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646863</v>
+        <v>646921</v>
       </c>
       <c r="R10" t="n">
-        <v>7037660</v>
+        <v>7037745</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,6 +1611,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1628,7 +1633,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1639,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113715167</v>
+        <v>113715163</v>
       </c>
       <c r="B11" t="n">
         <v>90135</v>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646935</v>
+        <v>646932</v>
       </c>
       <c r="R11" t="n">
-        <v>7037814</v>
+        <v>7037691</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113715168</v>
+        <v>113713933</v>
       </c>
       <c r="B12" t="n">
-        <v>90416</v>
+        <v>97402</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646943</v>
+        <v>646971</v>
       </c>
       <c r="R12" t="n">
-        <v>7037813</v>
+        <v>7037815</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,6 +1826,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113713927</v>
+        <v>113711819</v>
       </c>
       <c r="B13" t="n">
-        <v>90135</v>
+        <v>90320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>646932</v>
+        <v>646993</v>
       </c>
       <c r="R13" t="n">
-        <v>7037691</v>
+        <v>7037776</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1946,7 +1956,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1957,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711790</v>
+        <v>113711818</v>
       </c>
       <c r="B14" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646842</v>
+        <v>646982</v>
       </c>
       <c r="R14" t="n">
-        <v>7037658</v>
+        <v>7037768</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113713939</v>
+        <v>113711795</v>
       </c>
       <c r="B15" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646993</v>
+        <v>646800</v>
       </c>
       <c r="R15" t="n">
-        <v>7037796</v>
+        <v>7037819</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2141,11 +2151,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2000 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2163,7 +2168,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2174,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711797</v>
+        <v>113711817</v>
       </c>
       <c r="B16" t="n">
         <v>90416</v>
@@ -2214,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646826</v>
+        <v>646966</v>
       </c>
       <c r="R16" t="n">
-        <v>7037814</v>
+        <v>7037793</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113715147</v>
+        <v>113711813</v>
       </c>
       <c r="B17" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646783</v>
+        <v>646935</v>
       </c>
       <c r="R17" t="n">
-        <v>7037810</v>
+        <v>7037814</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,7 +2380,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2386,7 +2391,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113715160</v>
+        <v>113711806</v>
       </c>
       <c r="B18" t="n">
         <v>90135</v>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2492,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113713917</v>
+        <v>113713919</v>
       </c>
       <c r="B19" t="n">
         <v>90135</v>
@@ -2532,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646892</v>
+        <v>646842</v>
       </c>
       <c r="R19" t="n">
-        <v>7037818</v>
+        <v>7037747</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113715146</v>
+        <v>113715143</v>
       </c>
       <c r="B20" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2614,21 +2619,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646801</v>
+        <v>646869</v>
       </c>
       <c r="R20" t="n">
-        <v>7037720</v>
+        <v>7037654</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2704,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113715145</v>
+        <v>113713930</v>
       </c>
       <c r="B21" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,21 +2725,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2744,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646798</v>
+        <v>646938</v>
       </c>
       <c r="R21" t="n">
-        <v>7037685</v>
+        <v>7037784</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2810,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113711788</v>
+        <v>113713918</v>
       </c>
       <c r="B22" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2853,7 +2858,7 @@
         <v>646869</v>
       </c>
       <c r="R22" t="n">
-        <v>7037654</v>
+        <v>7037783</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2910,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2916,7 +2921,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113713925</v>
+        <v>113713940</v>
       </c>
       <c r="B23" t="n">
         <v>97402</v>
@@ -2956,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646916</v>
+        <v>647007</v>
       </c>
       <c r="R23" t="n">
-        <v>7037675</v>
+        <v>7037798</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,7 +3001,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>150 orkidéer ca</t>
+          <t>400 orkidéer ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113711823</v>
+        <v>113715153</v>
       </c>
       <c r="B24" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,25 +3044,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3067,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>647016</v>
+        <v>646892</v>
       </c>
       <c r="R24" t="n">
-        <v>7037806</v>
+        <v>7037818</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3105,11 +3110,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>100 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3138,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113711820</v>
+        <v>113713908</v>
       </c>
       <c r="B25" t="n">
-        <v>97402</v>
+        <v>78201</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,25 +3150,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646995</v>
+        <v>646842</v>
       </c>
       <c r="R25" t="n">
-        <v>7037777</v>
+        <v>7037658</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3216,11 +3216,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3238,7 +3233,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3249,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113715157</v>
+        <v>113713925</v>
       </c>
       <c r="B26" t="n">
-        <v>90153</v>
+        <v>97402</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646862</v>
+        <v>646916</v>
       </c>
       <c r="R26" t="n">
-        <v>7037725</v>
+        <v>7037675</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3325,6 +3320,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>150 orkidéer ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113711802</v>
+        <v>113711794</v>
       </c>
       <c r="B27" t="n">
-        <v>90146</v>
+        <v>90320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,25 +3367,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>48</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646857</v>
+        <v>646778</v>
       </c>
       <c r="R27" t="n">
-        <v>7037736</v>
+        <v>7037818</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113711798</v>
+        <v>113711797</v>
       </c>
       <c r="B28" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646856</v>
+        <v>646826</v>
       </c>
       <c r="R28" t="n">
-        <v>7037838</v>
+        <v>7037814</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113713922</v>
+        <v>113713906</v>
       </c>
       <c r="B29" t="n">
         <v>90135</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646871</v>
+        <v>646863</v>
       </c>
       <c r="R29" t="n">
-        <v>7037737</v>
+        <v>7037660</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113715165</v>
+        <v>113713914</v>
       </c>
       <c r="B30" t="n">
-        <v>90135</v>
+        <v>56826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3689,21 +3689,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646956</v>
+        <v>646810</v>
       </c>
       <c r="R30" t="n">
-        <v>7037763</v>
+        <v>7037810</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3749,6 +3749,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En hona</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,10 +3784,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113713912</v>
+        <v>113711823</v>
       </c>
       <c r="B31" t="n">
-        <v>90320</v>
+        <v>97402</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3795,21 +3800,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646778</v>
+        <v>647016</v>
       </c>
       <c r="R31" t="n">
-        <v>7037818</v>
+        <v>7037806</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3857,6 +3862,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>100 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3874,7 +3884,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3885,7 +3895,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113715170</v>
+        <v>113713939</v>
       </c>
       <c r="B32" t="n">
         <v>97402</v>
@@ -3925,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646978</v>
+        <v>646993</v>
       </c>
       <c r="R32" t="n">
-        <v>7037805</v>
+        <v>7037796</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3965,7 +3975,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>200 orkidéer ca</t>
+          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3996,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113715154</v>
+        <v>113713921</v>
       </c>
       <c r="B33" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4012,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4036,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646869</v>
+        <v>646862</v>
       </c>
       <c r="R33" t="n">
-        <v>7037783</v>
+        <v>7037725</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4102,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113711796</v>
+        <v>113715147</v>
       </c>
       <c r="B34" t="n">
-        <v>56826</v>
+        <v>90416</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,21 +4128,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4142,7 +4152,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646810</v>
+        <v>646783</v>
       </c>
       <c r="R34" t="n">
         <v>7037810</v>
@@ -4180,11 +4190,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>En hona</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4202,7 +4207,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4213,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113715149</v>
+        <v>113711814</v>
       </c>
       <c r="B35" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4234,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646800</v>
+        <v>646943</v>
       </c>
       <c r="R35" t="n">
-        <v>7037819</v>
+        <v>7037813</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4308,7 +4313,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4319,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113711815</v>
+        <v>113713929</v>
       </c>
       <c r="B36" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4331,25 +4336,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4359,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646971</v>
+        <v>646956</v>
       </c>
       <c r="R36" t="n">
-        <v>7037815</v>
+        <v>7037763</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4397,11 +4402,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -4218,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113711814</v>
+        <v>113713929</v>
       </c>
       <c r="B35" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4234,21 +4234,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646943</v>
+        <v>646956</v>
       </c>
       <c r="R35" t="n">
-        <v>7037813</v>
+        <v>7037763</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4324,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113713929</v>
+        <v>113711814</v>
       </c>
       <c r="B36" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4340,21 +4340,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646956</v>
+        <v>646943</v>
       </c>
       <c r="R36" t="n">
-        <v>7037763</v>
+        <v>7037813</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113715158</v>
+        <v>113713923</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>56917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646871</v>
+        <v>646921</v>
       </c>
       <c r="R2" t="n">
-        <v>7037737</v>
+        <v>7037745</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711810</v>
+        <v>113713934</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646948</v>
+        <v>646978</v>
       </c>
       <c r="R3" t="n">
-        <v>7037705</v>
+        <v>7037805</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,6 +864,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>200 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -876,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713910</v>
+        <v>113711496</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646801</v>
+        <v>647016</v>
       </c>
       <c r="R4" t="n">
-        <v>7037720</v>
+        <v>7037806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,6 +975,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>100 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113715152</v>
+        <v>113713939</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646856</v>
+        <v>646993</v>
       </c>
       <c r="R5" t="n">
-        <v>7037838</v>
+        <v>7037796</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113715170</v>
+        <v>113711814</v>
       </c>
       <c r="B6" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646978</v>
+        <v>646943</v>
       </c>
       <c r="R6" t="n">
-        <v>7037805</v>
+        <v>7037813</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1177,11 +1197,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>200 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1199,7 +1214,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1210,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113711820</v>
+        <v>113713921</v>
       </c>
       <c r="B7" t="n">
-        <v>97402</v>
+        <v>90153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646995</v>
+        <v>646862</v>
       </c>
       <c r="R7" t="n">
-        <v>7037777</v>
+        <v>7037725</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1288,11 +1303,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1321,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113715145</v>
+        <v>113711806</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646798</v>
+        <v>646948</v>
       </c>
       <c r="R8" t="n">
-        <v>7037685</v>
+        <v>7037706</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1416,7 +1426,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1427,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113711802</v>
+        <v>113715146</v>
       </c>
       <c r="B9" t="n">
-        <v>90146</v>
+        <v>90135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646857</v>
+        <v>646801</v>
       </c>
       <c r="R9" t="n">
-        <v>7037736</v>
+        <v>7037720</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,7 +1532,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1533,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113711805</v>
+        <v>113713929</v>
       </c>
       <c r="B10" t="n">
-        <v>56917</v>
+        <v>90135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646921</v>
+        <v>646956</v>
       </c>
       <c r="R10" t="n">
-        <v>7037745</v>
+        <v>7037763</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,11 +1621,6 @@
           <t>2023-10-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett orädd par i  sitt häckningsrevir och födosöksområde</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1638,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1644,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113715163</v>
+        <v>113713927</v>
       </c>
       <c r="B11" t="n">
         <v>90135</v>
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113713933</v>
+        <v>113715143</v>
       </c>
       <c r="B12" t="n">
-        <v>97402</v>
+        <v>78201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646971</v>
+        <v>646869</v>
       </c>
       <c r="R12" t="n">
-        <v>7037815</v>
+        <v>7037654</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1826,11 +1831,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113711819</v>
+        <v>113713937</v>
       </c>
       <c r="B13" t="n">
         <v>90320</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1967,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113711818</v>
+        <v>113713919</v>
       </c>
       <c r="B14" t="n">
         <v>90135</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646982</v>
+        <v>646842</v>
       </c>
       <c r="R14" t="n">
-        <v>7037768</v>
+        <v>7037747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113711795</v>
+        <v>113715154</v>
       </c>
       <c r="B15" t="n">
         <v>90135</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646800</v>
+        <v>646869</v>
       </c>
       <c r="R15" t="n">
-        <v>7037819</v>
+        <v>7037783</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2179,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113711817</v>
+        <v>113711813</v>
       </c>
       <c r="B16" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646966</v>
+        <v>646935</v>
       </c>
       <c r="R16" t="n">
-        <v>7037793</v>
+        <v>7037814</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113711813</v>
+        <v>113711795</v>
       </c>
       <c r="B17" t="n">
         <v>90135</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646935</v>
+        <v>646800</v>
       </c>
       <c r="R17" t="n">
-        <v>7037814</v>
+        <v>7037819</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113711806</v>
+        <v>113715158</v>
       </c>
       <c r="B18" t="n">
         <v>90135</v>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646948</v>
+        <v>646871</v>
       </c>
       <c r="R18" t="n">
-        <v>7037706</v>
+        <v>7037737</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113713919</v>
+        <v>113715156</v>
       </c>
       <c r="B19" t="n">
-        <v>90135</v>
+        <v>90146</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646842</v>
+        <v>646857</v>
       </c>
       <c r="R19" t="n">
-        <v>7037747</v>
+        <v>7037736</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113715143</v>
+        <v>113713938</v>
       </c>
       <c r="B20" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646869</v>
+        <v>646995</v>
       </c>
       <c r="R20" t="n">
-        <v>7037654</v>
+        <v>7037777</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2679,6 +2679,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2709,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113713930</v>
+        <v>113711807</v>
       </c>
       <c r="B21" t="n">
-        <v>90135</v>
+        <v>97402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646938</v>
+        <v>646916</v>
       </c>
       <c r="R21" t="n">
-        <v>7037784</v>
+        <v>7037675</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2787,6 +2792,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>150 orkidéer ca</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2804,7 +2814,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2815,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113713918</v>
+        <v>113715148</v>
       </c>
       <c r="B22" t="n">
-        <v>90135</v>
+        <v>90320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2837,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646869</v>
+        <v>646778</v>
       </c>
       <c r="R22" t="n">
-        <v>7037783</v>
+        <v>7037818</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2921,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113713940</v>
+        <v>113713915</v>
       </c>
       <c r="B23" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,25 +2943,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2971,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>647007</v>
+        <v>646826</v>
       </c>
       <c r="R23" t="n">
-        <v>7037798</v>
+        <v>7037814</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2997,11 +3007,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>400 orkidéer ca</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113715153</v>
+        <v>113713914</v>
       </c>
       <c r="B24" t="n">
-        <v>90135</v>
+        <v>56826</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,21 +3053,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646892</v>
+        <v>646810</v>
       </c>
       <c r="R24" t="n">
-        <v>7037818</v>
+        <v>7037810</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3108,6 +3113,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En hona</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113713908</v>
+        <v>113715153</v>
       </c>
       <c r="B25" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,21 +3164,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646842</v>
+        <v>646892</v>
       </c>
       <c r="R25" t="n">
-        <v>7037658</v>
+        <v>7037818</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113713925</v>
+        <v>113715147</v>
       </c>
       <c r="B26" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3266,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646916</v>
+        <v>646783</v>
       </c>
       <c r="R26" t="n">
-        <v>7037675</v>
+        <v>7037810</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3320,11 +3330,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>150 orkidéer ca</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113711794</v>
+        <v>113713909</v>
       </c>
       <c r="B27" t="n">
-        <v>90320</v>
+        <v>78201</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,25 +3372,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646778</v>
+        <v>646798</v>
       </c>
       <c r="R27" t="n">
-        <v>7037818</v>
+        <v>7037685</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3450,7 +3455,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3461,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113711797</v>
+        <v>113713908</v>
       </c>
       <c r="B28" t="n">
-        <v>90416</v>
+        <v>78201</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646826</v>
+        <v>646842</v>
       </c>
       <c r="R28" t="n">
-        <v>7037814</v>
+        <v>7037658</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3556,7 +3561,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3567,7 +3572,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113713906</v>
+        <v>113713930</v>
       </c>
       <c r="B29" t="n">
         <v>90135</v>
@@ -3607,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646863</v>
+        <v>646938</v>
       </c>
       <c r="R29" t="n">
-        <v>7037660</v>
+        <v>7037784</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3673,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113713914</v>
+        <v>113711495</v>
       </c>
       <c r="B30" t="n">
-        <v>56826</v>
+        <v>97402</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,25 +3690,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3718,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646810</v>
+        <v>647007</v>
       </c>
       <c r="R30" t="n">
-        <v>7037810</v>
+        <v>7037798</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3753,7 +3758,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>En hona</t>
+          <t>400 orkidéer ca</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,7 +3778,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3784,7 +3789,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113711823</v>
+        <v>113711815</v>
       </c>
       <c r="B31" t="n">
         <v>97402</v>
@@ -3824,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>647016</v>
+        <v>646971</v>
       </c>
       <c r="R31" t="n">
-        <v>7037806</v>
+        <v>7037815</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3864,7 +3869,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>100 orkidéer ca</t>
+          <t>250 orkidéer ca</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113713939</v>
+        <v>113713936</v>
       </c>
       <c r="B32" t="n">
-        <v>97402</v>
+        <v>90135</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3907,25 +3912,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646993</v>
+        <v>646982</v>
       </c>
       <c r="R32" t="n">
-        <v>7037796</v>
+        <v>7037768</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3971,11 +3976,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2000 orkidéer ca</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113713921</v>
+        <v>113713906</v>
       </c>
       <c r="B33" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646862</v>
+        <v>646863</v>
       </c>
       <c r="R33" t="n">
-        <v>7037725</v>
+        <v>7037660</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113715147</v>
+        <v>113711798</v>
       </c>
       <c r="B34" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4128,21 +4128,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646783</v>
+        <v>646856</v>
       </c>
       <c r="R34" t="n">
-        <v>7037810</v>
+        <v>7037838</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4218,7 +4218,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113713929</v>
+        <v>113711810</v>
       </c>
       <c r="B35" t="n">
         <v>90135</v>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646956</v>
+        <v>646948</v>
       </c>
       <c r="R35" t="n">
-        <v>7037763</v>
+        <v>7037705</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4324,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113711814</v>
+        <v>113713935</v>
       </c>
       <c r="B36" t="n">
         <v>90416</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646943</v>
+        <v>646966</v>
       </c>
       <c r="R36" t="n">
-        <v>7037813</v>
+        <v>7037793</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46958-2023 artfynd.xlsx
+++ b/artfynd/A 46958-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711794</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711819</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711793</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711797</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711814</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711817</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711497</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711787</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711792</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711795</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711798</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711799</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711800</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711804</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711806</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711809</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711810</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711811</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711812</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711813</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711818</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711802</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711788</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711790</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711791</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3505,6 +3645,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711796</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3611,6 +3756,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711498</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3717,6 +3867,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711805</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3823,6 +3978,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711494</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3929,6 +4089,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711495</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4035,6 +4200,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711496</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4141,6 +4311,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711807</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4247,6 +4422,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711815</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4353,6 +4533,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711816</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4459,8 +4644,52 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113711820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>